--- a/artfynd/A 24492-2023 artfynd.xlsx
+++ b/artfynd/A 24492-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 24492-2023 artfynd.xlsx
+++ b/artfynd/A 24492-2023 artfynd.xlsx
@@ -3744,7 +3744,7 @@
         <v>121265083</v>
       </c>
       <c r="B26" t="n">
-        <v>91443</v>
+        <v>91453</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>

--- a/artfynd/A 24492-2023 artfynd.xlsx
+++ b/artfynd/A 24492-2023 artfynd.xlsx
@@ -3744,7 +3744,7 @@
         <v>121265083</v>
       </c>
       <c r="B26" t="n">
-        <v>91453</v>
+        <v>91465</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>

--- a/artfynd/A 24492-2023 artfynd.xlsx
+++ b/artfynd/A 24492-2023 artfynd.xlsx
@@ -3744,7 +3744,7 @@
         <v>121265083</v>
       </c>
       <c r="B26" t="n">
-        <v>91465</v>
+        <v>91466</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>

--- a/artfynd/A 24492-2023 artfynd.xlsx
+++ b/artfynd/A 24492-2023 artfynd.xlsx
@@ -3744,7 +3744,7 @@
         <v>121265083</v>
       </c>
       <c r="B26" t="n">
-        <v>91466</v>
+        <v>91469</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>

--- a/artfynd/A 24492-2023 artfynd.xlsx
+++ b/artfynd/A 24492-2023 artfynd.xlsx
@@ -3744,7 +3744,7 @@
         <v>121265083</v>
       </c>
       <c r="B26" t="n">
-        <v>91469</v>
+        <v>91475</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>

--- a/artfynd/A 24492-2023 artfynd.xlsx
+++ b/artfynd/A 24492-2023 artfynd.xlsx
@@ -3744,7 +3744,7 @@
         <v>121265083</v>
       </c>
       <c r="B26" t="n">
-        <v>91475</v>
+        <v>91476</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>

--- a/artfynd/A 24492-2023 artfynd.xlsx
+++ b/artfynd/A 24492-2023 artfynd.xlsx
@@ -3335,12 +3335,7 @@
         <v>108739846</v>
       </c>
       <c r="B23" t="n">
-        <v>89350</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91850</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3375,16 +3370,18 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kopphagen, V om Almunge kyrka, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>665781.9148788844</v>
+        <v>665782</v>
       </c>
       <c r="R23" t="n">
-        <v>6640428.56831849</v>
+        <v>6640429</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3414,24 +3411,14 @@
           <t>2023-04-28</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-04-28</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ca. 10 ex. i övervallade stamsår på levande ek, omkr. 219 cm.</t>
+          <t>Ca. 10 ex. på levande ek, omkr. 219 cm.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3440,6 +3427,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3455,7 +3443,7 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Övervallade stamsår på levande ek, omkr. 219 cm. # Skogsek</t>
+          <t>Stammen av levande ek, omkr. 219 cm. # Skogsek</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>

--- a/artfynd/A 24492-2023 artfynd.xlsx
+++ b/artfynd/A 24492-2023 artfynd.xlsx
@@ -3335,7 +3335,7 @@
         <v>108739846</v>
       </c>
       <c r="B23" t="n">
-        <v>91850</v>
+        <v>91856</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 24492-2023 artfynd.xlsx
+++ b/artfynd/A 24492-2023 artfynd.xlsx
@@ -3335,7 +3335,7 @@
         <v>108739846</v>
       </c>
       <c r="B23" t="n">
-        <v>91856</v>
+        <v>91866</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 24492-2023 artfynd.xlsx
+++ b/artfynd/A 24492-2023 artfynd.xlsx
@@ -3335,7 +3335,7 @@
         <v>108739846</v>
       </c>
       <c r="B23" t="n">
-        <v>91866</v>
+        <v>91867</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 24492-2023 artfynd.xlsx
+++ b/artfynd/A 24492-2023 artfynd.xlsx
@@ -3335,7 +3335,7 @@
         <v>108739846</v>
       </c>
       <c r="B23" t="n">
-        <v>91867</v>
+        <v>91868</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 24492-2023 artfynd.xlsx
+++ b/artfynd/A 24492-2023 artfynd.xlsx
@@ -3335,7 +3335,7 @@
         <v>108739846</v>
       </c>
       <c r="B23" t="n">
-        <v>91868</v>
+        <v>91870</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 24492-2023 artfynd.xlsx
+++ b/artfynd/A 24492-2023 artfynd.xlsx
@@ -3335,7 +3335,7 @@
         <v>108739846</v>
       </c>
       <c r="B23" t="n">
-        <v>91870</v>
+        <v>91871</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 24492-2023 artfynd.xlsx
+++ b/artfynd/A 24492-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>83319578</v>
+        <v>111924482</v>
       </c>
       <c r="B2" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89799</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220785</v>
+        <v>37</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Jättekamskivling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Amanita ceciliae</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Berk. &amp; Broome) Bas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,19 +708,25 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Länna Bruk, Upl</t>
+          <t>Norra Kopphagen, Norra Kopphagen, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>665852.41991464</v>
+        <v>665746</v>
       </c>
       <c r="R2" t="n">
-        <v>6640800.310107508</v>
+        <v>6640603</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,29 +748,24 @@
           <t>Almunge</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>EC913F56-11F5-4151-9CED-2AC9B4BEE5B5</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2004-02-02</t>
+          <t>2023-09-06</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2004-02-02</t>
+          <t>2023-09-06</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,73 +780,69 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Niina Sallmén, Nina Söderström</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Trädportalen</t>
-        </is>
-      </c>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>83319583</v>
+        <v>79689447</v>
       </c>
       <c r="B3" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80703</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220785</v>
+        <v>226</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skuggorangelav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Caloplaca lucifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>G.Thor</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>cm²</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Länna Bruk, Upl</t>
+          <t>Länna, SSV om bruket, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>665850.1931234341</v>
+        <v>665665</v>
       </c>
       <c r="R3" t="n">
-        <v>6640816.300712348</v>
+        <v>6640548</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,29 +864,14 @@
           <t>Almunge</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>ABFC2F12-CD6B-4D25-B05A-F0FED0BF86BB</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2004-02-02</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-09-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2004-02-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-09-21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,35 +882,41 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Bryn mellan granskog och öppnare yta med frihuggna ekar.</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Gammal ek</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Gammal ek</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Mattias Lif</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Niina Sallmén, Nina Söderström</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Trädportalen</t>
-        </is>
-      </c>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>63205991</v>
+        <v>121265083</v>
       </c>
       <c r="B4" t="n">
-        <v>5426</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -941,37 +924,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101410</v>
+        <v>366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Marma, Upl</t>
+          <t>Östra Kopphagen, Östra Kopphagen, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>665718.1137974027</v>
+        <v>665800</v>
       </c>
       <c r="R4" t="n">
-        <v>6640649.988275247</v>
+        <v>6640427</v>
       </c>
       <c r="S4" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -995,27 +978,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1999-01-01</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2001-12-31</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>gamla spår, Marma 0907, mittpunkt inventerat område</t>
+          <t>På fälld asp</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,27 +1013,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Per Stolpe</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Pär Eriksson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>79689435</v>
+        <v>104064213</v>
       </c>
       <c r="B5" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92134</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1058,43 +1036,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>1106</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Peck) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Länna, SSV om Länna bruk, Upl</t>
+          <t>Östra Kopphagen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>665808.2747589021</v>
+        <v>665803</v>
       </c>
       <c r="R5" t="n">
-        <v>6640649.998926339</v>
+        <v>6640439</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,22 +1091,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2018-03-25</t>
+          <t>2022-10-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2018-03-25</t>
+          <t>2022-10-12</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,31 +1117,16 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>Äldre tall</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Äldre tall</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mattias Lif</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mattias Lif</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1181,12 +1136,7 @@
         <v>79689388</v>
       </c>
       <c r="B6" t="n">
-        <v>89953</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92510</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1227,10 +1177,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>665760.086358085</v>
+        <v>665760</v>
       </c>
       <c r="R6" t="n">
-        <v>6640477.375759288</v>
+        <v>6640477</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1260,19 +1210,9 @@
           <t>2018-04-13</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2018-04-13</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1309,50 +1249,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>79689413</v>
+        <v>92237296</v>
       </c>
       <c r="B7" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92510</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2671</v>
+        <v>1143</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Blekticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Haploporus tuberculosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Fr.) Niemelä &amp; Y.C.Dai</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Länna, SSV om Länna bruk, Upl</t>
+          <t>Länna, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>665781.9415776248</v>
+        <v>665778</v>
       </c>
       <c r="R7" t="n">
-        <v>6640664.408736807</v>
+        <v>6640550</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1379,22 +1323,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2018-03-28</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2018-03-28</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1406,9 +1340,14 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>På död gren ca 8 m upp på levande skogsek</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Klippa</t>
+          <t>På död gren ca 8 m upp på levande skogsek</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1426,42 +1365,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>79689450</v>
+        <v>75085744</v>
       </c>
       <c r="B8" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>1205</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1471,14 +1405,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Länna, SSV om bruket, Upl</t>
+          <t>Kopphagen 6,5 km V om Almunge kyrka, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>665811.335807211</v>
+        <v>665512</v>
       </c>
       <c r="R8" t="n">
-        <v>6640649.130217819</v>
+        <v>6640613</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1505,22 +1439,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2017-09-21</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-04-26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2017-09-21</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-04-26</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>7 ex. på stammen av levande asp, omkr. 149 cm.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1532,80 +1461,79 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Äldre blandskog</t>
-        </is>
-      </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>Tall, omkrets 136 cm i brösthöjd</t>
+          <t>Asp</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Tall, omkrets 136 cm i brösthöjd</t>
+          <t>Stammen av levande asp. # Asp</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Mattias Lif</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mattias Lif</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>79689410</v>
+        <v>79689411</v>
       </c>
       <c r="B9" t="n">
-        <v>76907</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6436</v>
+        <v>1467</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gulpudrad spiklav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Calicium adspersum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Pers.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Länna, SSV om Länna bruk, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>665768.9537363068</v>
+        <v>665769</v>
       </c>
       <c r="R9" t="n">
-        <v>6640594.435177838</v>
+        <v>6640594</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1635,19 +1563,9 @@
           <t>2018-03-28</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2018-03-28</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1684,15 +1602,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>79689411</v>
+        <v>79689414</v>
       </c>
       <c r="B10" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1719,12 +1632,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>cm²</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1733,10 +1646,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>665768.9537363068</v>
+        <v>665782</v>
       </c>
       <c r="R10" t="n">
-        <v>6640594.435177838</v>
+        <v>6640664</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1766,21 +1679,11 @@
           <t>2018-03-28</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2018-03-28</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1792,12 +1695,12 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>Grov ek (438 cm i omkrets vid brösthöjd)</t>
+          <t>Ek (omkrets vid brösthöjd 183 cm)</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Grov ek (438 cm i omkrets vid brösthöjd)</t>
+          <t>Ek (omkrets vid brösthöjd 183 cm)</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1815,15 +1718,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>79689434</v>
+        <v>79689448</v>
       </c>
       <c r="B11" t="n">
-        <v>89350</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1831,43 +1729,43 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5445</v>
+        <v>1467</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Länna, SSV om Länna bruk, Upl</t>
+          <t>Länna, SSV om bruket, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>665763.6325961901</v>
+        <v>665665</v>
       </c>
       <c r="R11" t="n">
-        <v>6640454.402551393</v>
+        <v>6640548</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1894,22 +1792,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2018-03-25</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-09-21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2018-03-25</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-09-21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1921,14 +1809,19 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Bryn mellan granskog och öppnare yta med frihuggna ekar.</t>
+        </is>
+      </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>Ek, 202 cm i omkrets vid brösthöjd</t>
+          <t>Gammal ek</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Ek, 202 cm i omkrets vid brösthöjd</t>
+          <t>Gammal ek</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1946,15 +1839,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>79689417</v>
+        <v>79689413</v>
       </c>
       <c r="B12" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1986,10 +1874,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>665786.8610216558</v>
+        <v>665782</v>
       </c>
       <c r="R12" t="n">
-        <v>6640441.864229864</v>
+        <v>6640664</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2019,21 +1907,11 @@
           <t>2018-03-28</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2018-03-28</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2043,19 +1921,9 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>På nedfallen ekgren (från grov ek, 318 cm i omkrets vid bh).</t>
-        </is>
-      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>På nedfallen ekgren (från grov ek, 318 cm i omkrets vid bh).</t>
+          <t>Klippa</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2073,15 +1941,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>79689416</v>
+        <v>79689417</v>
       </c>
       <c r="B13" t="n">
-        <v>78458</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2089,43 +1952,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6457</v>
+        <v>2671</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Länna, SSV om Länna bruk, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>665786.9184968509</v>
+        <v>665787</v>
       </c>
       <c r="R13" t="n">
-        <v>6640485.616203433</v>
+        <v>6640442</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2155,21 +2009,11 @@
           <t>2018-03-28</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2018-03-28</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2181,17 +2025,17 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Lövrik liten berghöjd</t>
+          <t>Blandskog</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>Senvuxen asp (omkrets vid brösthöjd 39 cm)</t>
+          <t>På nedfallen ekgren (från grov ek, 318 cm i omkrets vid bh).</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Senvuxen asp (omkrets vid brösthöjd 39 cm)</t>
+          <t>På nedfallen ekgren (från grov ek, 318 cm i omkrets vid bh).</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2209,59 +2053,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>79689414</v>
+        <v>92237250</v>
       </c>
       <c r="B14" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89083</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1467</v>
+        <v>4377</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Blodvaxing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Hygrocybe coccinea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>cm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Länna, SSV om Länna bruk, Upl</t>
+          <t>Länna bruksgata 43, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>665781.9415776248</v>
+        <v>665871</v>
       </c>
       <c r="R14" t="n">
-        <v>6640664.408736807</v>
+        <v>6640678</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2288,22 +2127,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2018-03-28</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2018-03-28</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2314,16 +2143,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>Ek (omkrets vid brösthöjd 183 cm)</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Ek (omkrets vid brösthöjd 183 cm)</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2340,15 +2159,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>79689390</v>
+        <v>92237249</v>
       </c>
       <c r="B15" t="n">
-        <v>78458</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2356,43 +2170,43 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6457</v>
+        <v>5420</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Länna, SSV om Länna bruk, Upl</t>
+          <t>Länna bruksgata, V om, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>665795.7913825006</v>
+        <v>665828</v>
       </c>
       <c r="R15" t="n">
-        <v>6640523.727775178</v>
+        <v>6640655</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2419,22 +2233,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2018-04-13</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2018-04-13</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2445,16 +2249,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>Senvuxen asp, omkrets 72 cm vid brösthöjd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Senvuxen asp, omkrets 72 cm vid brösthöjd</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2471,15 +2265,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>79689415</v>
+        <v>79689435</v>
       </c>
       <c r="B16" t="n">
-        <v>89350</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2487,26 +2276,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5445</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2520,10 +2309,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>665781.9415776248</v>
+        <v>665808</v>
       </c>
       <c r="R16" t="n">
-        <v>6640664.408736807</v>
+        <v>6640650</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2550,22 +2339,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2018-03-28</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-03-25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2018-03-28</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-03-25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2577,14 +2356,19 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>Ek (omkrets vid brösthöjd 183 cm)</t>
+          <t>Äldre tall</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Ek (omkrets vid brösthöjd 183 cm)</t>
+          <t>Äldre tall</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2602,15 +2386,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>92237296</v>
+        <v>79689450</v>
       </c>
       <c r="B17" t="n">
-        <v>89953</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2618,43 +2397,43 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1143</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blekticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Haploporus tuberculosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä &amp; Y.C.Dai</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Länna, Upl</t>
+          <t>Länna, SSV om bruket, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>665777.9896790289</v>
+        <v>665811</v>
       </c>
       <c r="R17" t="n">
-        <v>6640550.085598352</v>
+        <v>6640649</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2681,22 +2460,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2020-06-28</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-09-21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2020-06-28</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-09-21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2708,14 +2477,19 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Äldre blandskog</t>
+        </is>
+      </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>På död gren ca 8 m upp på levande skogsek</t>
+          <t>Tall, omkrets 136 cm i brösthöjd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>På död gren ca 8 m upp på levande skogsek</t>
+          <t>Tall, omkrets 136 cm i brösthöjd</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2733,15 +2507,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>92237240</v>
+        <v>79689415</v>
       </c>
       <c r="B18" t="n">
-        <v>89350</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91867</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2768,7 +2537,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2778,14 +2547,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Länna, Upl</t>
+          <t>Länna, SSV om Länna bruk, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>665799.1270138796</v>
+        <v>665782</v>
       </c>
       <c r="R18" t="n">
-        <v>6640494.208234423</v>
+        <v>6640664</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2812,22 +2581,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2021-01-08</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-03-28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2021-01-08</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-03-28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2838,6 +2597,16 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>Ek (omkrets vid brösthöjd 183 cm)</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Ek (omkrets vid brösthöjd 183 cm)</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2854,42 +2623,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>92237249</v>
+        <v>79689434</v>
       </c>
       <c r="B19" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91867</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5420</v>
+        <v>5445</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2899,14 +2663,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Länna bruksgata, V om, Upl</t>
+          <t>Länna, SSV om Länna bruk, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>665828.2026586269</v>
+        <v>665764</v>
       </c>
       <c r="R19" t="n">
-        <v>6640654.91343839</v>
+        <v>6640454</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2933,22 +2697,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2020-10-13</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-03-25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2020-10-13</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-03-25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2959,6 +2713,16 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>Ek, 202 cm i omkrets vid brösthöjd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Ek, 202 cm i omkrets vid brösthöjd</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2975,47 +2739,42 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>92237258</v>
+        <v>92237240</v>
       </c>
       <c r="B20" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91867</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222771</v>
+        <v>5445</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -3024,10 +2783,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>665829.832042611</v>
+        <v>665799</v>
       </c>
       <c r="R20" t="n">
-        <v>6640517.20522938</v>
+        <v>6640494</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3054,22 +2813,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2020-09-05</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-01-08</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2020-09-05</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-01-08</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3096,15 +2845,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>100236695</v>
+        <v>108739846</v>
       </c>
       <c r="B21" t="n">
-        <v>56401</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91932</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3112,45 +2856,45 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100048</v>
+        <v>5445</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Norra Kopphagen, Upl</t>
+          <t>Kopphagen, V om Almunge kyrka, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>665700.6857162456</v>
+        <v>665782</v>
       </c>
       <c r="R21" t="n">
-        <v>6640600.433028453</v>
+        <v>6640429</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3177,22 +2921,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2022-04-26</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>09:27</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2022-04-26</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>09:27</t>
+          <t>2023-04-28</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ca. 10 ex. på levande ek, omkr. 219 cm.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3201,69 +2940,79 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Blandskog, (f.d. hagmark).</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>Skogsek</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Stammen av levande ek, omkr. 219 cm. # Skogsek</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Gillis Aronsson, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>104064213</v>
+        <v>79689410</v>
       </c>
       <c r="B22" t="n">
-        <v>89588</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78728</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1106</v>
+        <v>6436</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Gulpudrad spiklav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Calicium adspersum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Östra Kopphagen, Upl</t>
+          <t>Länna, SSV om Länna bruk, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>665802.6024453864</v>
+        <v>665769</v>
       </c>
       <c r="R22" t="n">
-        <v>6640439.048418968</v>
+        <v>6640594</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3290,22 +3039,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>13:48</t>
+          <t>2018-03-28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>13:48</t>
+          <t>2018-03-28</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3316,72 +3055,80 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>Grov ek (438 cm i omkrets vid brösthöjd)</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Grov ek (438 cm i omkrets vid brösthöjd)</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Mattias Lif</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Mattias Lif</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>108739846</v>
+        <v>79689390</v>
       </c>
       <c r="B23" t="n">
-        <v>91876</v>
+        <v>80367</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5445</v>
+        <v>6457</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kopphagen, V om Almunge kyrka, Upl</t>
+          <t>Länna, SSV om Länna bruk, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>665782</v>
+        <v>665796</v>
       </c>
       <c r="R23" t="n">
-        <v>6640429</v>
+        <v>6640524</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3408,17 +3155,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
+          <t>2018-04-13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ca. 10 ex. på levande ek, omkr. 219 cm.</t>
+          <t>2018-04-13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3427,49 +3169,38 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Blandskog, (f.d. hagmark).</t>
-        </is>
-      </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>Skogsek</t>
+          <t>Senvuxen asp, omkrets 72 cm vid brösthöjd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Stammen av levande ek, omkr. 219 cm. # Skogsek</t>
+          <t>Senvuxen asp, omkrets 72 cm vid brösthöjd</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Mattias Lif</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Gillis Aronsson, Cajsa Björkén</t>
+          <t>Mattias Lif</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>108739844</v>
+        <v>79689416</v>
       </c>
       <c r="B24" t="n">
-        <v>81962</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80367</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3477,43 +3208,43 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>232272</v>
+        <v>6457</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Scharlakansskål</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcoscypha austriaca</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Beck) Boud.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kopphagen, V om Almunge kyrka, Upl</t>
+          <t>Länna, SSV om Länna bruk, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>665713.3113371596</v>
+        <v>665787</v>
       </c>
       <c r="R24" t="n">
-        <v>6640644.745087468</v>
+        <v>6640486</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3540,27 +3271,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-03-28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ca. 5 ex. på nedfallen hägg-gren, på fuktig mark intill ett brett dike.</t>
+          <t>2018-03-28</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3569,53 +3285,43 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Igenväxande f.d. hagmark.</t>
+          <t>Lövrik liten berghöjd</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>Hägg</t>
+          <t>Senvuxen asp (omkrets vid brösthöjd 39 cm)</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Nedfallen hägg-gren, på fuktig mark. # Hägg</t>
+          <t>Senvuxen asp (omkrets vid brösthöjd 39 cm)</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Mattias Lif</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Gillis Aronsson, Cajsa Björkén</t>
+          <t>Mattias Lif</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>111924482</v>
+        <v>92237239</v>
       </c>
       <c r="B25" t="n">
-        <v>84876</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3623,44 +3329,43 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>37</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Jättekamskivling</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Amanita ceciliae</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Berk. &amp; Broome) Bas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Norra Kopphagen (Norra Kopphagen), Upl</t>
+          <t>Länna, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>665746</v>
+        <v>665663</v>
       </c>
       <c r="R25" t="n">
-        <v>6640603</v>
+        <v>6640545</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3687,22 +3392,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>10:18</t>
+          <t>2021-01-21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>10:18</t>
+          <t>2021-01-21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3717,27 +3412,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Mattias Lif</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Mattias Lif</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121265083</v>
+        <v>100236695</v>
       </c>
       <c r="B26" t="n">
-        <v>91476</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3745,34 +3435,45 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>366</v>
+        <v>100048</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Östra Kopphagen, Östra Kopphagen, Upl</t>
+          <t>Norra Kopphagen, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>665800</v>
+        <v>665701</v>
       </c>
       <c r="R26" t="n">
-        <v>6640427</v>
+        <v>6640600</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3799,27 +3500,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2022-04-26</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2022-04-26</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:23</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På fälld asp</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3843,6 +3539,1273 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>63205991</v>
+      </c>
+      <c r="B27" t="n">
+        <v>5495</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Marma, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>665718</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6640650</v>
+      </c>
+      <c r="S27" t="n">
+        <v>75</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>1999-01-01</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2001-12-31</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>gamla spår, Marma 0907, mittpunkt inventerat område</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Per Stolpe</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Pär Eriksson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>75654639</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57947</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Länna Bruksgata, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>665932</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6640789</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2019-01-10</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2019-01-10</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>113315645</v>
+      </c>
+      <c r="B29" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>SV Länna Bruk., Länna, Almunge, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>665744</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6640865</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2023-11-19</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2023-11-19</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>85600787</v>
+      </c>
+      <c r="B30" t="n">
+        <v>58586</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>103051</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Rosenfink</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Carpodacus erythrinus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Pallas, 1770)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>SV Länna Bruk., Länna, Almunge, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>665744</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6640865</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2020-05-20</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2020-05-20</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>108643310</v>
+      </c>
+      <c r="B31" t="n">
+        <v>58826</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>208242</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lissotriton vulgaris</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Länna bruksgata 45, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>665880</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6640607</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2023-05-01</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2023-05-01</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>I liten trädgårdsdamm</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>83319578</v>
+      </c>
+      <c r="B32" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Länna Bruk, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>665852</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6640800</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>EC913F56-11F5-4151-9CED-2AC9B4BEE5B5</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2004-02-02</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2004-02-02</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Niina Sallmén, Nina Söderström</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>83319583</v>
+      </c>
+      <c r="B33" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Länna Bruk, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>665850</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6640816</v>
+      </c>
+      <c r="S33" t="n">
+        <v>25</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>ABFC2F12-CD6B-4D25-B05A-F0FED0BF86BB</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2004-02-02</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2004-02-02</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Niina Sallmén, Nina Söderström</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>83319590</v>
+      </c>
+      <c r="B34" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Länna Bruk, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>665934</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6640849</v>
+      </c>
+      <c r="S34" t="n">
+        <v>25</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>9D2A4A85-D96C-4194-8B0A-9B0297A30E98</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2004-02-02</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2004-02-02</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Niina Sallmén, Nina Söderström</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>70868808</v>
+      </c>
+      <c r="B35" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Länna Bruksgata, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>665932</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6640789</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2018-04-25</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2018-04-25</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>92237258</v>
+      </c>
+      <c r="B36" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Länna, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>665830</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6640517</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2020-09-05</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2020-09-05</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>108739844</v>
+      </c>
+      <c r="B37" t="n">
+        <v>84148</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>232272</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Scharlakansskål</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Sarcoscypha austriaca</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Beck) Boud.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Kopphagen, V om Almunge kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>665713</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6640644</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2023-04-28</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2023-04-28</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ca. 5 ex. på nedfallen hägg-gren, på fuktig mark intill ett brett dike.</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Igenväxande f.d. hagmark.</t>
+        </is>
+      </c>
+      <c r="AL37" t="inlineStr">
+        <is>
+          <t>Hägg</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Nedfallen hägg-gren, på fuktig mark. # Hägg</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson, Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
